--- a/datos/cartolas.xlsx
+++ b/datos/cartolas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\germanleiks\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\germanleiks\Documents\PPC\Proyectos\P14_Descarga_Cartolas\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{333B2785-0761-49E9-B459-7D8BEAE214DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32200A7A-DB51-473A-90DF-82D35850B8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7C66449D-BEC7-4532-B7B8-DE81207D3308}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>Número de cartola</t>
-  </si>
-  <si>
     <t>Aguas Araucanía</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>Aguas Chañar</t>
+  </si>
+  <si>
+    <t>Numero_Cartola</t>
   </si>
 </sst>
 </file>
@@ -456,15 +456,15 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C2" s="2">
         <v>10001</v>
@@ -472,10 +472,10 @@
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C3" s="2">
         <v>10002</v>
@@ -483,10 +483,10 @@
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="C4" s="2">
         <v>10003</v>
